--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484216_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484216_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2677</v>
+        <v>2.0345</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9708</v>
+        <v>2.4652</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7030999999999999</v>
+        <v>-0.4307</v>
       </c>
       <c r="G2" t="n">
         <v>1.0575</v>
@@ -610,13 +610,13 @@
         <v>2.1488</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6328</v>
+        <v>-0.866</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2726</v>
+        <v>-0.233</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9053</v>
+        <v>-0.633</v>
       </c>
       <c r="V2" t="n">
         <v>3.601</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.246</v>
+        <v>1.8997</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3534</v>
+        <v>2.2523</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1075</v>
+        <v>-0.3526</v>
       </c>
       <c r="G3" t="n">
         <v>1.1209</v>
@@ -688,13 +688,13 @@
         <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4414</v>
+        <v>-0.7876</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4621</v>
+        <v>-0.5632</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0207</v>
+        <v>-0.2245</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3869</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1126</v>
+        <v>1.1824</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3048</v>
+        <v>1.8104</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1923</v>
+        <v>-0.628</v>
       </c>
       <c r="G4" t="n">
         <v>0.9398</v>
@@ -766,13 +766,13 @@
         <v>1.9534</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6236</v>
+        <v>-0.5538</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0289</v>
+        <v>-0.5233</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4053</v>
+        <v>-0.0305</v>
       </c>
       <c r="V4" t="n">
         <v>1.7731</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6704</v>
+        <v>-0.4603</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0435</v>
+        <v>1.1446</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7138</v>
+        <v>-1.6049</v>
       </c>
       <c r="G5" t="n">
         <v>1.7359</v>
@@ -844,13 +844,13 @@
         <v>0.7814</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2342</v>
+        <v>-1.0242</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5915</v>
+        <v>-0.4903</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6428</v>
+        <v>-0.5339</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6763</v>
+        <v>-0.7968</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8484</v>
+        <v>-1.0506</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1721</v>
+        <v>0.2538</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0213</v>
@@ -922,13 +922,13 @@
         <v>1.5627</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2289</v>
+        <v>-0.3495</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0384</v>
+        <v>-0.2406</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1905</v>
+        <v>-0.1088</v>
       </c>
       <c r="V6" t="n">
         <v>0.9414</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0406</v>
+        <v>-1.7955</v>
       </c>
       <c r="E8" t="n">
         <v>-0.9119</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1287</v>
+        <v>-0.8835</v>
       </c>
       <c r="G8" t="n">
         <v>0.1382</v>
@@ -1078,13 +1078,13 @@
         <v>1.9534</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5341</v>
+        <v>-1.289</v>
       </c>
       <c r="T8" t="n">
         <v>-0.5364</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9978</v>
+        <v>-0.7527</v>
       </c>
       <c r="V8" t="n">
         <v>0.3321</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1398</v>
+        <v>-1.9648</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0471</v>
+        <v>-0.8449</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0927</v>
+        <v>-1.1199</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1231</v>
@@ -1156,13 +1156,13 @@
         <v>0.3907</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-0.5916</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5309</v>
+        <v>-0.3287</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2356</v>
+        <v>-0.2629</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6642</v>
@@ -1192,10 +1192,10 @@
         <v>-1.451000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>3.9289</v>
+        <v>3.928899999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.38</v>
+        <v>-5.379799999999999</v>
       </c>
       <c r="G10" t="n">
         <v>4.2744</v>
@@ -1234,13 +1234,13 @@
         <v>10.7438</v>
       </c>
       <c r="S10" t="n">
-        <v>-5.461600000000001</v>
+        <v>-5.4617</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.9156</v>
+        <v>-2.9155</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.546</v>
+        <v>-2.5463</v>
       </c>
       <c r="V10" t="n">
         <v>5.5965</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.9849</v>
+        <v>4.3112</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4968</v>
+        <v>4.4911</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4881</v>
+        <v>-0.1799</v>
       </c>
       <c r="G11" t="n">
-        <v>3.5437</v>
+        <v>2.3088</v>
       </c>
       <c r="H11" t="n">
-        <v>3.0988</v>
+        <v>2.7677</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4449</v>
+        <v>-0.4589</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8983</v>
+        <v>4.0116</v>
       </c>
       <c r="K11" t="n">
-        <v>3.318</v>
+        <v>3.9307</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5803</v>
+        <v>0.0809</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3546</v>
+        <v>-1.7028</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2192</v>
+        <v>-1.163</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1354</v>
+        <v>-0.5399</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1377</v>
+        <v>0.617</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5752</v>
+        <v>0.4795</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5625</v>
+        <v>0.1375</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.6732</v>
+        <v>-0.1773</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.6732</v>
+        <v>-0.1773</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.6534</v>
+        <v>4.1355</v>
       </c>
       <c r="E12" t="n">
-        <v>4.9967</v>
+        <v>3.1934</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3433</v>
+        <v>0.9421</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3088</v>
+        <v>3.5437</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7677</v>
+        <v>3.0988</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4589</v>
+        <v>0.4449</v>
       </c>
       <c r="J12" t="n">
-        <v>4.0116</v>
+        <v>3.8983</v>
       </c>
       <c r="K12" t="n">
-        <v>3.9307</v>
+        <v>3.318</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0809</v>
+        <v>0.5803</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7028</v>
+        <v>-0.3546</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.163</v>
+        <v>-0.2192</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5399</v>
+        <v>-0.1354</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9592000000000001</v>
+        <v>1.2883</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9851</v>
+        <v>0.2718</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0259</v>
+        <v>1.0165</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1773</v>
+        <v>-1.6732</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1773</v>
+        <v>-1.6732</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.3616</v>
+        <v>3.6105</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4339</v>
+        <v>2.7373</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9277</v>
+        <v>0.8732</v>
       </c>
       <c r="G13" t="n">
         <v>1.6667</v>
@@ -1468,13 +1468,13 @@
         <v>1.9534</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5635</v>
+        <v>0.8124</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0384</v>
+        <v>0.2649</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6019</v>
+        <v>0.5474</v>
       </c>
       <c r="V13" t="n">
         <v>0.1548</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3054</v>
+        <v>2.1991</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8793</v>
+        <v>1.4749</v>
       </c>
       <c r="F14" t="n">
-        <v>0.426</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>0.9866</v>
@@ -1546,13 +1546,13 @@
         <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9454</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9383</v>
+        <v>0.5339</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0071</v>
+        <v>0.3053</v>
       </c>
       <c r="V14" t="n">
         <v>0.7641</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0527</v>
+        <v>1.2264</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1623</v>
+        <v>2.3646</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1096</v>
+        <v>-1.1382</v>
       </c>
       <c r="G15" t="n">
         <v>0.6415999999999999</v>
@@ -1624,13 +1624,13 @@
         <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0121</v>
+        <v>0.1857</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1127</v>
+        <v>0.0895</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1248</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-1.1638</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0982</v>
+        <v>-0.3686</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7943</v>
+        <v>-1.0977</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8925</v>
+        <v>0.7291</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2759</v>
@@ -1702,13 +1702,13 @@
         <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7234</v>
+        <v>1.2567</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7567</v>
+        <v>0.4534</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9667</v>
+        <v>0.8033</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1773</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2539</v>
+        <v>-0.5028</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8168</v>
+        <v>0.5135</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0708</v>
+        <v>-1.0163</v>
       </c>
       <c r="G17" t="n">
         <v>-1.2945</v>
@@ -1780,13 +1780,13 @@
         <v>0.3907</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6499</v>
+        <v>0.401</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6136</v>
+        <v>0.3102</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.8195</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2951</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.645</v>
+        <v>-0.7267</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6002</v>
@@ -1858,13 +1858,13 @@
         <v>0.1953</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1876</v>
+        <v>0.3081</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0605</v>
+        <v>0.1417</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2481</v>
+        <v>0.1664</v>
       </c>
       <c r="V18" t="n">
         <v>0.2772</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5694</v>
+        <v>-1.1843</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3122</v>
+        <v>0.6156</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8816</v>
+        <v>-1.7999</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5481</v>
@@ -1936,13 +1936,13 @@
         <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4435</v>
+        <v>-0.0584</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3631</v>
+        <v>-0.0598</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0803</v>
+        <v>0.0014</v>
       </c>
       <c r="V19" t="n">
         <v>-1.1638</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7491</v>
+        <v>-3.0173</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8300999999999999</v>
+        <v>-1.2345</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.919</v>
+        <v>-1.7828</v>
       </c>
       <c r="G20" t="n">
         <v>-2.9132</v>
@@ -2014,13 +2014,13 @@
         <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4293</v>
+        <v>0.161</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4404</v>
+        <v>0.0359</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0111</v>
+        <v>0.1251</v>
       </c>
       <c r="V20" t="n">
         <v>-1.8279</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4287</v>
+        <v>-3.4264</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.3084</v>
+        <v>-3.9039</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1203</v>
+        <v>0.4775</v>
       </c>
       <c r="G21" t="n">
         <v>-4.5036</v>
@@ -2092,13 +2092,13 @@
         <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7064</v>
+        <v>0.2958</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.341</v>
+        <v>0.0634</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3654</v>
+        <v>0.2324</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.0641</v>
+        <v>-4.0387</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4904</v>
+        <v>-3.6815</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5737</v>
+        <v>-0.3572</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2862</v>
@@ -2170,13 +2170,13 @@
         <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9965000000000001</v>
+        <v>0.0289</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.0384</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1492</v>
+        <v>0.0673</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6093</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.451000000000001</v>
+        <v>2.125099999999997</v>
       </c>
       <c r="E23" t="n">
-        <v>5.379700000000001</v>
+        <v>5.379999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.929</v>
+        <v>-3.2548</v>
       </c>
       <c r="G23" t="n">
         <v>-4.274299999999998</v>
@@ -2248,13 +2248,13 @@
         <v>16.6039</v>
       </c>
       <c r="S23" t="n">
-        <v>5.4617</v>
+        <v>6.135699999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5463</v>
+        <v>2.546</v>
       </c>
       <c r="U23" t="n">
-        <v>2.9155</v>
+        <v>3.589599999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-5.5965</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484216_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484216_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,7 @@
       <c r="X10" t="n">
         <v>-1.773</v>
       </c>
+      <c r="Y10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1375,11 @@
       <c r="X11" t="n">
         <v>-0.1773</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1458,11 @@
       <c r="X12" t="n">
         <v>-1.6732</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0.1548</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.4545</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,11 +1707,16 @@
       <c r="X15" t="n">
         <v>-1.1638</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3686</v>
+        <v>0.921</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0977</v>
+        <v>0.921</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7291</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2759</v>
+        <v>0.921</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0039</v>
+        <v>0.921</v>
       </c>
       <c r="I16" t="n">
-        <v>0.728</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1018</v>
+        <v>0.921</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3735</v>
+        <v>0.921</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7284</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3777</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3773</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0004</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2567</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4534</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8033</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1773</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4545</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5028</v>
+        <v>-0.3686</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5135</v>
+        <v>-1.0977</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0163</v>
+        <v>0.7291</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2945</v>
+        <v>-0.2759</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1461</v>
+        <v>-1.0039</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1484</v>
+        <v>0.728</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2033</v>
+        <v>1.1018</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0819</v>
+        <v>0.3735</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1214</v>
+        <v>0.7284</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4978</v>
+        <v>-1.3777</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2279</v>
+        <v>-1.3773</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2698</v>
+        <v>-0.0004</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3907</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>0.401</v>
+        <v>1.2567</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3102</v>
+        <v>0.4534</v>
       </c>
       <c r="U17" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.8033</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.1773</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.4545</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8195</v>
+        <v>-0.5028</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.09279999999999999</v>
+        <v>0.5135</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7267</v>
+        <v>-1.0163</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.6002</v>
+        <v>-1.2945</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4518</v>
+        <v>-1.1461</v>
       </c>
       <c r="I18" t="n">
         <v>-0.1484</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5118</v>
+        <v>0.2033</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6332</v>
+        <v>0.0819</v>
       </c>
       <c r="L18" t="n">
         <v>0.1214</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0885</v>
+        <v>-1.4978</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8186</v>
+        <v>-1.2279</v>
       </c>
       <c r="O18" t="n">
         <v>-0.2698</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3081</v>
+        <v>0.401</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1417</v>
+        <v>0.3102</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1664</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>A. RUIZ CANAMERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1843</v>
+        <v>-0.8195</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6156</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7999</v>
+        <v>-0.7267</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5481</v>
+        <v>-1.6002</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2612</v>
+        <v>-1.4518</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8093</v>
+        <v>-0.1484</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6754</v>
+        <v>-0.5118</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6754</v>
+        <v>-0.6332</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.1214</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2235</v>
+        <v>-1.0885</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4142</v>
+        <v>-0.8186</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8093</v>
+        <v>-0.2698</v>
       </c>
       <c r="P19" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0584</v>
+        <v>0.3081</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0598</v>
+        <v>0.1417</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0014</v>
+        <v>0.1664</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1638</v>
+        <v>0.2772</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1638</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0173</v>
+        <v>-1.1843</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2345</v>
+        <v>0.6156</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7828</v>
+        <v>-1.7999</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.9132</v>
+        <v>-0.5481</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.713</v>
+        <v>0.2612</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2002</v>
+        <v>-0.8093</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2704</v>
+        <v>0.6754</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6102</v>
+        <v>0.6754</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6603</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6427</v>
+        <v>-1.2235</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1028</v>
+        <v>-0.4142</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5399</v>
+        <v>-0.8093</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>0.161</v>
+        <v>-0.0584</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0359</v>
+        <v>-0.0598</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1251</v>
+        <v>0.0014</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8279</v>
+        <v>-1.1638</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.8279</v>
+        <v>-1.1638</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4264</v>
+        <v>-3.0173</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.9039</v>
+        <v>-1.2345</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4775</v>
+        <v>-1.7828</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.5036</v>
+        <v>-2.9132</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7936</v>
+        <v>-1.713</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.71</v>
+        <v>-1.2002</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.9907</v>
+        <v>-1.2704</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9555</v>
+        <v>-0.6102</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.0351</v>
+        <v>-0.6603</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5129</v>
+        <v>-1.6427</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.838</v>
+        <v>-1.1028</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.5399</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2958</v>
+        <v>0.161</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0634</v>
+        <v>0.0359</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2324</v>
+        <v>0.1251</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0387</v>
+        <v>-3.4264</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6815</v>
+        <v>-3.9039</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3572</v>
+        <v>0.4775</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2862</v>
+        <v>-4.5036</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7752</v>
+        <v>-1.7936</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.0614</v>
+        <v>-2.71</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.713</v>
+        <v>-2.9907</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2689</v>
+        <v>-0.9555</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.9818</v>
+        <v>-2.0351</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5733</v>
+        <v>-1.5129</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4937</v>
+        <v>-0.838</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0795</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
         <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0289</v>
+        <v>0.2958</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0384</v>
+        <v>0.0634</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0673</v>
+        <v>0.2324</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,152 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.125099999999997</v>
+        <v>-4.9596</v>
       </c>
       <c r="E23" t="n">
-        <v>5.379999999999999</v>
+        <v>-4.6025</v>
       </c>
       <c r="F23" t="n">
+        <v>-0.3572</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-3.2072</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.1458</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-3.0614</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1.6339</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-1.9818</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.5733</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.4937</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-1.0795</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.0384</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.0673</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484216_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.125199999999999</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5.379999999999998</v>
+      </c>
+      <c r="F24" t="n">
         <v>-3.2548</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G24" t="n">
         <v>-4.274299999999998</v>
       </c>
-      <c r="H23" t="n">
-        <v>3.816799999999999</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="H24" t="n">
+        <v>3.8168</v>
+      </c>
+      <c r="I24" t="n">
         <v>-8.091100000000001</v>
       </c>
-      <c r="J23" t="n">
-        <v>11.8043</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="J24" t="n">
+        <v>11.8044</v>
+      </c>
+      <c r="K24" t="n">
         <v>13.822</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L24" t="n">
         <v>-2.0173</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M24" t="n">
         <v>-16.0789</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N24" t="n">
         <v>-10.0049</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O24" t="n">
         <v>-6.0738</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P24" t="n">
         <v>5.859999999999999</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q24" t="n">
         <v>-10.7437</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>16.6039</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S24" t="n">
         <v>6.135699999999999</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>2.546</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>3.589599999999999</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V24" t="n">
         <v>-5.5965</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W24" t="n">
         <v>1.773</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X24" t="n">
         <v>-7.369499999999999</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
